--- a/src/test/resources/Data/Credit_Card_TestData_Final.xlsx
+++ b/src/test/resources/Data/Credit_Card_TestData_Final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shine.shiju\Downloads\Credit-Card-CreditCardAPI_Testing\src\test\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089FCAAC-FF5F-4D13-911C-1E6DE9C138D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4772C7F-7040-4194-AECC-55BB8B16ACAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -928,9 +928,6 @@
     <t>Security</t>
   </si>
   <si>
-    <t>Verify unauthorized user cannot access another user’s credit card</t>
-  </si>
-  <si>
     <t>USER_ATTACKER</t>
   </si>
   <si>
@@ -1228,9 +1225,6 @@
     <t>CC_TC_068</t>
   </si>
   <si>
-    <t>Verify unauthorized user cannot inspect another card penalty state via statement</t>
-  </si>
-  <si>
     <t>No dedicated penalty endpoint; statement is available API path to verify ownership boundary.</t>
   </si>
   <si>
@@ -2774,6 +2768,12 @@
   </si>
   <si>
     <t>Verify low credit score and high DTI causes rejection</t>
+  </si>
+  <si>
+    <t>Verify blocked card purchase rejection</t>
+  </si>
+  <si>
+    <t>Verify overdue notification generation</t>
   </si>
 </sst>
 </file>
@@ -3261,10 +3261,10 @@
         <v>22</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="Y1" s="13" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="Z1" s="13" t="s">
         <v>23</v>
@@ -5799,7 +5799,7 @@
         <v>169</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>195</v>
@@ -7086,7 +7086,7 @@
         <v>20000</v>
       </c>
       <c r="Y47" s="16">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="Z47" s="16"/>
       <c r="AA47" s="16"/>
@@ -7223,7 +7223,7 @@
       <c r="H49" s="16"/>
       <c r="I49" s="17"/>
       <c r="J49" s="16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="K49" s="16"/>
       <c r="L49" s="16">
@@ -7232,13 +7232,13 @@
       <c r="M49" s="16"/>
       <c r="N49" s="16"/>
       <c r="O49" s="16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="P49" s="16" t="s">
         <v>44</v>
       </c>
       <c r="Q49" s="16" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="R49" s="16" t="s">
         <v>43</v>
@@ -7262,13 +7262,13 @@
       <c r="AA49" s="16"/>
       <c r="AB49" s="19"/>
       <c r="AC49" s="19" t="s">
+        <v>858</v>
+      </c>
+      <c r="AD49" s="19" t="s">
+        <v>859</v>
+      </c>
+      <c r="AE49" s="19" t="s">
         <v>860</v>
-      </c>
-      <c r="AD49" s="19" t="s">
-        <v>861</v>
-      </c>
-      <c r="AE49" s="19" t="s">
-        <v>862</v>
       </c>
       <c r="AF49" s="19" t="s">
         <v>48</v>
@@ -7308,7 +7308,7 @@
       <c r="H50" s="16"/>
       <c r="I50" s="17"/>
       <c r="J50" s="16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="K50" s="16"/>
       <c r="L50" s="16">
@@ -7317,13 +7317,13 @@
       <c r="M50" s="16"/>
       <c r="N50" s="16"/>
       <c r="O50" s="16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="P50" s="16" t="s">
         <v>44</v>
       </c>
       <c r="Q50" s="16" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="R50" s="16" t="s">
         <v>265</v>
@@ -7347,13 +7347,13 @@
       <c r="AA50" s="16"/>
       <c r="AB50" s="19"/>
       <c r="AC50" s="19" t="s">
+        <v>861</v>
+      </c>
+      <c r="AD50" s="19" t="s">
+        <v>862</v>
+      </c>
+      <c r="AE50" s="19" t="s">
         <v>863</v>
-      </c>
-      <c r="AD50" s="19" t="s">
-        <v>864</v>
-      </c>
-      <c r="AE50" s="19" t="s">
-        <v>865</v>
       </c>
       <c r="AF50" s="19" t="s">
         <v>48</v>
@@ -7370,22 +7370,22 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>299</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>301</v>
+        <v>293</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>915</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>302</v>
+        <v>264</v>
       </c>
       <c r="G51" s="16" t="s">
         <v>39</v>
@@ -7393,7 +7393,7 @@
       <c r="H51" s="16"/>
       <c r="I51" s="17"/>
       <c r="J51" s="16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="K51" s="16"/>
       <c r="L51" s="16">
@@ -7402,13 +7402,13 @@
       <c r="M51" s="16"/>
       <c r="N51" s="16"/>
       <c r="O51" s="16" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="P51" s="16" t="s">
         <v>44</v>
       </c>
       <c r="Q51" s="16" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="R51" s="16" t="s">
         <v>265</v>
@@ -7427,21 +7427,21 @@
         <v>46177</v>
       </c>
       <c r="X51" s="16" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="Y51" s="16"/>
       <c r="Z51" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AA51" s="16" t="s">
         <v>251</v>
       </c>
       <c r="AB51" s="19"/>
       <c r="AC51" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="AD51" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="AD51" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="AE51" s="19"/>
       <c r="AF51" s="19" t="s">
@@ -7459,19 +7459,19 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>298</v>
       </c>
       <c r="C52" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D52" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="E52" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>308</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>249</v>
@@ -7510,7 +7510,7 @@
         <v>50000</v>
       </c>
       <c r="R52" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S52" s="19">
         <v>50000</v>
@@ -7532,20 +7532,20 @@
       </c>
       <c r="Y52" s="19"/>
       <c r="Z52" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA52" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB52" s="19"/>
       <c r="AC52" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="AD52" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="AD52" s="19" t="s">
+      <c r="AE52" s="19" t="s">
         <v>312</v>
-      </c>
-      <c r="AE52" s="19" t="s">
-        <v>313</v>
       </c>
       <c r="AF52" s="19" t="s">
         <v>48</v>
@@ -7562,19 +7562,19 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B53" s="19" t="s">
         <v>298</v>
       </c>
       <c r="C53" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E53" s="19" t="s">
         <v>314</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>315</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>249</v>
@@ -7635,20 +7635,20 @@
       </c>
       <c r="Y53" s="19"/>
       <c r="Z53" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA53" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB53" s="19"/>
       <c r="AC53" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AD53" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="AE53" s="19" t="s">
         <v>316</v>
-      </c>
-      <c r="AE53" s="19" t="s">
-        <v>317</v>
       </c>
       <c r="AF53" s="19" t="s">
         <v>48</v>
@@ -7665,19 +7665,19 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>298</v>
       </c>
       <c r="C54" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E54" s="19" t="s">
         <v>318</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>319</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>249</v>
@@ -7716,7 +7716,7 @@
         <v>50000</v>
       </c>
       <c r="R54" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S54" s="19">
         <v>50000</v>
@@ -7738,22 +7738,22 @@
       </c>
       <c r="Y54" s="19"/>
       <c r="Z54" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA54" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB54" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="AC54" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="AC54" s="19" t="s">
+      <c r="AD54" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="AD54" s="19" t="s">
+      <c r="AE54" s="19" t="s">
         <v>322</v>
-      </c>
-      <c r="AE54" s="19" t="s">
-        <v>323</v>
       </c>
       <c r="AF54" s="19" t="s">
         <v>48</v>
@@ -7770,25 +7770,25 @@
     </row>
     <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>298</v>
       </c>
       <c r="C55" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E55" s="19" t="s">
         <v>324</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>325</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>249</v>
       </c>
       <c r="G55" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H55" s="19" t="s">
         <v>40</v>
@@ -7821,7 +7821,7 @@
         <v>50000</v>
       </c>
       <c r="R55" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S55" s="19">
         <v>50000</v>
@@ -7843,20 +7843,20 @@
       </c>
       <c r="Y55" s="19"/>
       <c r="Z55" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA55" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB55" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AC55" s="19"/>
       <c r="AD55" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="AE55" s="19" t="s">
         <v>328</v>
-      </c>
-      <c r="AE55" s="19" t="s">
-        <v>329</v>
       </c>
       <c r="AF55" s="19" t="s">
         <v>48</v>
@@ -7873,19 +7873,19 @@
     </row>
     <row r="56" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="C56" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="D56" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="E56" s="19" t="s">
         <v>333</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>334</v>
       </c>
       <c r="F56" s="19" t="s">
         <v>249</v>
@@ -7946,20 +7946,20 @@
       </c>
       <c r="Y56" s="19"/>
       <c r="Z56" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA56" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB56" s="19"/>
       <c r="AC56" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="AD56" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="AD56" s="19" t="s">
+      <c r="AE56" s="19" t="s">
         <v>336</v>
-      </c>
-      <c r="AE56" s="19" t="s">
-        <v>337</v>
       </c>
       <c r="AF56" s="19" t="s">
         <v>48</v>
@@ -7976,19 +7976,19 @@
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B57" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>331</v>
-      </c>
       <c r="C57" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>338</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>339</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>264</v>
@@ -8049,20 +8049,20 @@
       </c>
       <c r="Y57" s="19"/>
       <c r="Z57" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA57" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB57" s="19"/>
       <c r="AC57" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD57" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="AE57" s="19" t="s">
         <v>340</v>
-      </c>
-      <c r="AE57" s="19" t="s">
-        <v>341</v>
       </c>
       <c r="AF57" s="19" t="s">
         <v>48</v>
@@ -8079,19 +8079,19 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B58" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>331</v>
-      </c>
       <c r="C58" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>342</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>343</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>249</v>
@@ -8152,20 +8152,20 @@
       </c>
       <c r="Y58" s="19"/>
       <c r="Z58" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA58" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB58" s="19"/>
       <c r="AC58" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD58" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="AE58" s="19" t="s">
         <v>344</v>
-      </c>
-      <c r="AE58" s="19" t="s">
-        <v>345</v>
       </c>
       <c r="AF58" s="19" t="s">
         <v>48</v>
@@ -8182,19 +8182,19 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B59" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>331</v>
-      </c>
       <c r="C59" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E59" s="19" t="s">
         <v>346</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>347</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>249</v>
@@ -8255,22 +8255,22 @@
       </c>
       <c r="Y59" s="19"/>
       <c r="Z59" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA59" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB59" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC59" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="AC59" s="19" t="s">
+      <c r="AD59" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="AD59" s="19" t="s">
+      <c r="AE59" s="19" t="s">
         <v>350</v>
-      </c>
-      <c r="AE59" s="19" t="s">
-        <v>351</v>
       </c>
       <c r="AF59" s="19" t="s">
         <v>48</v>
@@ -8287,19 +8287,19 @@
     </row>
     <row r="60" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B60" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B60" s="19" t="s">
-        <v>331</v>
-      </c>
       <c r="C60" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E60" s="19" t="s">
         <v>352</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>353</v>
       </c>
       <c r="F60" s="19" t="s">
         <v>249</v>
@@ -8366,14 +8366,14 @@
         <v>251</v>
       </c>
       <c r="AB60" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AC60" s="19"/>
       <c r="AD60" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="AE60" s="19" t="s">
         <v>355</v>
-      </c>
-      <c r="AE60" s="19" t="s">
-        <v>356</v>
       </c>
       <c r="AF60" s="19" t="s">
         <v>48</v>
@@ -8390,25 +8390,25 @@
     </row>
     <row r="61" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B61" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B61" s="19" t="s">
-        <v>331</v>
-      </c>
       <c r="C61" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E61" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>358</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>249</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H61" s="19" t="s">
         <v>40</v>
@@ -8463,20 +8463,20 @@
       </c>
       <c r="Y61" s="19"/>
       <c r="Z61" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA61" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB61" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AC61" s="19"/>
       <c r="AD61" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="AE61" s="19" t="s">
         <v>360</v>
-      </c>
-      <c r="AE61" s="19" t="s">
-        <v>361</v>
       </c>
       <c r="AF61" s="19" t="s">
         <v>48</v>
@@ -8493,19 +8493,19 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B62" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="C62" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="D62" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="E62" s="19" t="s">
         <v>365</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>366</v>
       </c>
       <c r="F62" s="19" t="s">
         <v>277</v>
@@ -8566,20 +8566,20 @@
       </c>
       <c r="Y62" s="19"/>
       <c r="Z62" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA62" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB62" s="19"/>
       <c r="AC62" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="AD62" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="AD62" s="19" t="s">
+      <c r="AE62" s="19" t="s">
         <v>368</v>
-      </c>
-      <c r="AE62" s="19" t="s">
-        <v>369</v>
       </c>
       <c r="AF62" s="19" t="s">
         <v>233</v>
@@ -8596,19 +8596,19 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B63" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="B63" s="19" t="s">
-        <v>363</v>
-      </c>
       <c r="C63" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="E63" s="19" t="s">
         <v>370</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>371</v>
       </c>
       <c r="F63" s="19" t="s">
         <v>249</v>
@@ -8669,20 +8669,20 @@
       </c>
       <c r="Y63" s="19"/>
       <c r="Z63" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA63" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB63" s="19"/>
       <c r="AC63" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD63" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="AE63" s="19" t="s">
         <v>372</v>
-      </c>
-      <c r="AE63" s="19" t="s">
-        <v>373</v>
       </c>
       <c r="AF63" s="19" t="s">
         <v>233</v>
@@ -8699,19 +8699,19 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B64" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="B64" s="19" t="s">
-        <v>363</v>
-      </c>
       <c r="C64" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>374</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>375</v>
       </c>
       <c r="F64" s="19" t="s">
         <v>264</v>
@@ -8772,20 +8772,20 @@
       </c>
       <c r="Y64" s="19"/>
       <c r="Z64" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA64" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB64" s="19"/>
       <c r="AC64" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD64" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AE64" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="AE64" s="19" t="s">
-        <v>377</v>
       </c>
       <c r="AF64" s="19" t="s">
         <v>233</v>
@@ -8802,25 +8802,25 @@
     </row>
     <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>363</v>
-      </c>
       <c r="C65" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>378</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>379</v>
       </c>
       <c r="F65" s="19" t="s">
         <v>249</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H65" s="19" t="s">
         <v>40</v>
@@ -8875,20 +8875,20 @@
       </c>
       <c r="Y65" s="19"/>
       <c r="Z65" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA65" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB65" s="19"/>
       <c r="AC65" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="AD65" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="AD65" s="19" t="s">
+      <c r="AE65" s="19" t="s">
         <v>381</v>
-      </c>
-      <c r="AE65" s="19" t="s">
-        <v>382</v>
       </c>
       <c r="AF65" s="19" t="s">
         <v>233</v>
@@ -8905,19 +8905,19 @@
     </row>
     <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="C66" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="D66" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="E66" s="19" t="s">
         <v>386</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>387</v>
       </c>
       <c r="F66" s="19" t="s">
         <v>277</v>
@@ -8978,20 +8978,20 @@
       </c>
       <c r="Y66" s="19"/>
       <c r="Z66" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA66" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB66" s="19"/>
       <c r="AC66" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD66" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="AE66" s="19" t="s">
         <v>388</v>
-      </c>
-      <c r="AE66" s="19" t="s">
-        <v>389</v>
       </c>
       <c r="AF66" s="19" t="s">
         <v>233</v>
@@ -9008,19 +9008,19 @@
     </row>
     <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B67" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="B67" s="19" t="s">
-        <v>384</v>
-      </c>
       <c r="C67" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>390</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>391</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>277</v>
@@ -9081,20 +9081,20 @@
       </c>
       <c r="Y67" s="19"/>
       <c r="Z67" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA67" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB67" s="19"/>
       <c r="AC67" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AD67" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="AE67" s="19" t="s">
         <v>392</v>
-      </c>
-      <c r="AE67" s="19" t="s">
-        <v>393</v>
       </c>
       <c r="AF67" s="19" t="s">
         <v>233</v>
@@ -9111,19 +9111,19 @@
     </row>
     <row r="68" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B68" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="B68" s="19" t="s">
-        <v>384</v>
-      </c>
       <c r="C68" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>394</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="E68" s="19" t="s">
-        <v>395</v>
       </c>
       <c r="F68" s="19" t="s">
         <v>277</v>
@@ -9184,20 +9184,20 @@
       </c>
       <c r="Y68" s="19"/>
       <c r="Z68" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA68" s="19" t="s">
         <v>396</v>
-      </c>
-      <c r="AA68" s="19" t="s">
-        <v>397</v>
       </c>
       <c r="AB68" s="19"/>
       <c r="AC68" s="19" t="s">
         <v>279</v>
       </c>
       <c r="AD68" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="AE68" s="19" t="s">
         <v>398</v>
-      </c>
-      <c r="AE68" s="19" t="s">
-        <v>399</v>
       </c>
       <c r="AF68" s="19" t="s">
         <v>48</v>
@@ -9212,21 +9212,21 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B69" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="B69" s="19" t="s">
-        <v>384</v>
-      </c>
       <c r="C69" s="19" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>401</v>
+        <v>385</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>916</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>249</v>
@@ -9287,20 +9287,20 @@
       </c>
       <c r="Y69" s="19"/>
       <c r="Z69" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA69" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB69" s="19"/>
       <c r="AC69" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD69" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AE69" s="19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AF69" s="19" t="s">
         <v>48</v>
@@ -9317,22 +9317,22 @@
     </row>
     <row r="70" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C70" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="D70" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="E70" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="F70" s="19" t="s">
         <v>406</v>
-      </c>
-      <c r="E70" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>408</v>
       </c>
       <c r="G70" s="19" t="s">
         <v>39</v>
@@ -9353,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N70" s="19" t="s">
         <v>43</v>
@@ -9368,7 +9368,7 @@
         <v>150000</v>
       </c>
       <c r="R70" s="19" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="S70" s="19">
         <v>150000</v>
@@ -9390,20 +9390,20 @@
       </c>
       <c r="Y70" s="19"/>
       <c r="Z70" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA70" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB70" s="19"/>
       <c r="AC70" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="AD70" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="AE70" s="19" t="s">
         <v>411</v>
-      </c>
-      <c r="AD70" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="AE70" s="19" t="s">
-        <v>413</v>
       </c>
       <c r="AF70" s="19" t="s">
         <v>48</v>
@@ -9420,25 +9420,25 @@
     </row>
     <row r="71" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B71" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="D71" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C71" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="D71" s="19" t="s">
+      <c r="E71" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="F71" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>408</v>
-      </c>
       <c r="G71" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H71" s="19" t="s">
         <v>40</v>
@@ -9456,7 +9456,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N71" s="19" t="s">
         <v>43</v>
@@ -9493,20 +9493,20 @@
       </c>
       <c r="Y71" s="19"/>
       <c r="Z71" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA71" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB71" s="19"/>
       <c r="AC71" s="19" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AD71" s="19" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AE71" s="19" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AF71" s="19" t="s">
         <v>48</v>
@@ -9523,22 +9523,22 @@
     </row>
     <row r="72" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B72" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D72" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C72" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="D72" s="19" t="s">
+      <c r="E72" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="F72" s="19" t="s">
         <v>406</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>408</v>
       </c>
       <c r="G72" s="19" t="s">
         <v>39</v>
@@ -9559,7 +9559,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N72" s="19" t="s">
         <v>43</v>
@@ -9574,7 +9574,7 @@
         <v>150000</v>
       </c>
       <c r="R72" s="19" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="S72" s="19">
         <v>150000</v>
@@ -9596,20 +9596,20 @@
       </c>
       <c r="Y72" s="19"/>
       <c r="Z72" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA72" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB72" s="19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AC72" s="19"/>
       <c r="AD72" s="19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AE72" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AF72" s="19" t="s">
         <v>48</v>
@@ -9626,22 +9626,22 @@
     </row>
     <row r="73" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B73" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="D73" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C73" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="D73" s="19" t="s">
+      <c r="E73" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="F73" s="19" t="s">
         <v>406</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>424</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>408</v>
       </c>
       <c r="G73" s="19" t="s">
         <v>39</v>
@@ -9662,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N73" s="19" t="s">
         <v>43</v>
@@ -9677,7 +9677,7 @@
         <v>150000</v>
       </c>
       <c r="R73" s="19" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="S73" s="19">
         <v>150000</v>
@@ -9699,20 +9699,20 @@
       </c>
       <c r="Y73" s="19"/>
       <c r="Z73" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA73" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB73" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AC73" s="19"/>
       <c r="AD73" s="19" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AE73" s="19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AF73" s="19" t="s">
         <v>48</v>
@@ -9729,19 +9729,19 @@
     </row>
     <row r="74" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C74" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="D74" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="E74" s="19" t="s">
         <v>430</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>432</v>
       </c>
       <c r="F74" s="19" t="s">
         <v>249</v>
@@ -9811,13 +9811,13 @@
       </c>
       <c r="AB74" s="19"/>
       <c r="AC74" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="AD74" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="AE74" s="19" t="s">
         <v>433</v>
-      </c>
-      <c r="AD74" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="AE74" s="19" t="s">
-        <v>435</v>
       </c>
       <c r="AF74" s="19" t="s">
         <v>48</v>
@@ -9834,19 +9834,19 @@
     </row>
     <row r="75" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B75" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="D75" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C75" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>431</v>
-      </c>
       <c r="E75" s="19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F75" s="19" t="s">
         <v>277</v>
@@ -9909,20 +9909,20 @@
         <v>4500</v>
       </c>
       <c r="Z75" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA75" s="19" t="s">
         <v>396</v>
-      </c>
-      <c r="AA75" s="19" t="s">
-        <v>397</v>
       </c>
       <c r="AB75" s="19"/>
       <c r="AC75" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="AD75" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="AE75" s="19" t="s">
         <v>438</v>
-      </c>
-      <c r="AD75" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="AE75" s="19" t="s">
-        <v>440</v>
       </c>
       <c r="AF75" s="19" t="s">
         <v>48</v>
@@ -9939,19 +9939,19 @@
     </row>
     <row r="76" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B76" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D76" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C76" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>431</v>
-      </c>
       <c r="E76" s="19" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F76" s="19" t="s">
         <v>277</v>
@@ -10012,20 +10012,20 @@
       </c>
       <c r="Y76" s="19"/>
       <c r="Z76" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA76" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB76" s="19"/>
       <c r="AC76" s="19" t="s">
+        <v>864</v>
+      </c>
+      <c r="AD76" s="19" t="s">
+        <v>865</v>
+      </c>
+      <c r="AE76" s="19" t="s">
         <v>866</v>
-      </c>
-      <c r="AD76" s="19" t="s">
-        <v>867</v>
-      </c>
-      <c r="AE76" s="19" t="s">
-        <v>868</v>
       </c>
       <c r="AF76" s="19" t="s">
         <v>48</v>
@@ -10042,19 +10042,19 @@
     </row>
     <row r="77" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B77" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="D77" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C77" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>431</v>
-      </c>
       <c r="E77" s="19" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F77" s="19" t="s">
         <v>249</v>
@@ -10121,14 +10121,14 @@
         <v>251</v>
       </c>
       <c r="AB77" s="19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AC77" s="19"/>
       <c r="AD77" s="19" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AE77" s="19" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AF77" s="19" t="s">
         <v>48</v>
@@ -10145,19 +10145,19 @@
     </row>
     <row r="78" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B78" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="D78" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C78" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>431</v>
-      </c>
       <c r="E78" s="19" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F78" s="19" t="s">
         <v>277</v>
@@ -10218,20 +10218,20 @@
       </c>
       <c r="Y78" s="19"/>
       <c r="Z78" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA78" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB78" s="19" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AC78" s="19"/>
       <c r="AD78" s="19" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AE78" s="19" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AF78" s="19" t="s">
         <v>48</v>
@@ -10248,25 +10248,25 @@
     </row>
     <row r="79" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B79" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="D79" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>431</v>
-      </c>
       <c r="E79" s="19" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F79" s="19" t="s">
         <v>249</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H79" s="19" t="s">
         <v>40</v>
@@ -10321,20 +10321,20 @@
       </c>
       <c r="Y79" s="19"/>
       <c r="Z79" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA79" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AB79" s="19" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AC79" s="19"/>
       <c r="AD79" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AE79" s="19" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AF79" s="19" t="s">
         <v>48</v>
@@ -10351,19 +10351,19 @@
     </row>
     <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C80" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>459</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>461</v>
       </c>
       <c r="F80" s="19" t="s">
         <v>249</v>
@@ -10407,13 +10407,13 @@
       <c r="AA80" s="19"/>
       <c r="AB80" s="19"/>
       <c r="AC80" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="AD80" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="AE80" s="19" t="s">
         <v>462</v>
-      </c>
-      <c r="AD80" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="AE80" s="19" t="s">
-        <v>464</v>
       </c>
       <c r="AF80" s="19" t="s">
         <v>48</v>
@@ -10430,19 +10430,19 @@
     </row>
     <row r="81" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F81" s="19" t="s">
         <v>277</v>
@@ -10486,13 +10486,13 @@
       <c r="AA81" s="19"/>
       <c r="AB81" s="19"/>
       <c r="AC81" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD81" s="19" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AE81" s="19" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AF81" s="19" t="s">
         <v>48</v>
@@ -10509,19 +10509,19 @@
     </row>
     <row r="82" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F82" s="19" t="s">
         <v>277</v>
@@ -10565,13 +10565,13 @@
       <c r="AA82" s="19"/>
       <c r="AB82" s="19"/>
       <c r="AC82" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD82" s="19" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AE82" s="19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AF82" s="19" t="s">
         <v>48</v>
@@ -10588,19 +10588,19 @@
     </row>
     <row r="83" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F83" s="19" t="s">
         <v>277</v>
@@ -10650,13 +10650,13 @@
       </c>
       <c r="AB83" s="19"/>
       <c r="AC83" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD83" s="19" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AE83" s="19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AF83" s="19" t="s">
         <v>48</v>
@@ -10673,19 +10673,19 @@
     </row>
     <row r="84" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F84" s="19" t="s">
         <v>249</v>
@@ -10706,7 +10706,7 @@
       <c r="P84" s="19"/>
       <c r="Q84" s="19"/>
       <c r="R84" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S84" s="19">
         <v>50000</v>
@@ -10729,13 +10729,13 @@
       <c r="AA84" s="19"/>
       <c r="AB84" s="19"/>
       <c r="AC84" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD84" s="19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AE84" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AF84" s="19" t="s">
         <v>48</v>
@@ -10752,22 +10752,22 @@
     </row>
     <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G85" s="19" t="s">
         <v>39</v>
@@ -10808,13 +10808,13 @@
       <c r="AA85" s="19"/>
       <c r="AB85" s="19"/>
       <c r="AC85" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD85" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AE85" s="19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AF85" s="19" t="s">
         <v>48</v>
@@ -10831,19 +10831,19 @@
     </row>
     <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F86" s="19" t="s">
         <v>249</v>
@@ -10886,16 +10886,16 @@
       <c r="Z86" s="19"/>
       <c r="AA86" s="19"/>
       <c r="AB86" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC86" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="AD86" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="AC86" s="19" t="s">
+      <c r="AE86" s="19" t="s">
         <v>488</v>
-      </c>
-      <c r="AD86" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="AE86" s="19" t="s">
-        <v>490</v>
       </c>
       <c r="AF86" s="19" t="s">
         <v>48</v>
@@ -10912,19 +10912,19 @@
     </row>
     <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F87" s="19" t="s">
         <v>277</v>
@@ -10967,16 +10967,16 @@
       <c r="Z87" s="19"/>
       <c r="AA87" s="19"/>
       <c r="AB87" s="19" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AC87" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="AD87" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="AE87" s="19" t="s">
         <v>493</v>
-      </c>
-      <c r="AD87" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="AE87" s="19" t="s">
-        <v>495</v>
       </c>
       <c r="AF87" s="19" t="s">
         <v>48</v>
@@ -10993,19 +10993,19 @@
     </row>
     <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>291</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F88" s="19" t="s">
         <v>249</v>
@@ -11026,7 +11026,7 @@
       <c r="P88" s="19"/>
       <c r="Q88" s="19"/>
       <c r="R88" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S88" s="19">
         <v>50000</v>
@@ -11048,14 +11048,14 @@
       <c r="Z88" s="19"/>
       <c r="AA88" s="19"/>
       <c r="AB88" s="19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AC88" s="19"/>
       <c r="AD88" s="19" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AE88" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AF88" s="19" t="s">
         <v>48</v>
@@ -11075,22 +11075,22 @@
         <v>297</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D89" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E89" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="G89" s="19" t="s">
         <v>503</v>
-      </c>
-      <c r="F89" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>505</v>
       </c>
       <c r="H89" s="19"/>
       <c r="I89" s="25"/>
@@ -11116,13 +11116,13 @@
       <c r="AA89" s="19"/>
       <c r="AB89" s="19"/>
       <c r="AC89" s="19" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AD89" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AE89" s="19" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AF89" s="19" t="s">
         <v>48</v>
@@ -11142,22 +11142,22 @@
         <v>297</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D90" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F90" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="25"/>
@@ -11195,13 +11195,13 @@
       <c r="AA90" s="19"/>
       <c r="AB90" s="19"/>
       <c r="AC90" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AD90" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AE90" s="19" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AF90" s="19" t="s">
         <v>48</v>
@@ -11221,19 +11221,19 @@
         <v>297</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D91" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G91" s="19" t="s">
         <v>39</v>
@@ -11285,10 +11285,10 @@
         <v>252</v>
       </c>
       <c r="AD91" s="19" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AE91" s="19" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="AF91" s="19" t="s">
         <v>48</v>
@@ -11308,19 +11308,19 @@
         <v>297</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D92" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F92" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G92" s="19" t="s">
         <v>39</v>
@@ -11361,13 +11361,13 @@
       <c r="AA92" s="19"/>
       <c r="AB92" s="19"/>
       <c r="AC92" s="19" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="AD92" s="19" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="AE92" s="19" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="AF92" s="19" t="s">
         <v>48</v>
@@ -11387,19 +11387,19 @@
         <v>297</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D93" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G93" s="19" t="s">
         <v>39</v>
@@ -11417,7 +11417,7 @@
       <c r="P93" s="19"/>
       <c r="Q93" s="19"/>
       <c r="R93" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S93" s="19">
         <v>50000</v>
@@ -11440,13 +11440,13 @@
       <c r="AA93" s="19"/>
       <c r="AB93" s="19"/>
       <c r="AC93" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AD93" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AE93" s="19" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="AF93" s="19" t="s">
         <v>48</v>
@@ -11466,16 +11466,16 @@
         <v>297</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D94" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>249</v>
@@ -11507,13 +11507,13 @@
       <c r="AA94" s="19"/>
       <c r="AB94" s="19"/>
       <c r="AC94" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AD94" s="19" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="AE94" s="19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AF94" s="19" t="s">
         <v>48</v>
@@ -11533,19 +11533,19 @@
         <v>297</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D95" s="19" t="s">
         <v>300</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G95" s="19" t="s">
         <v>39</v>
@@ -11586,13 +11586,13 @@
       <c r="AA95" s="19"/>
       <c r="AB95" s="19"/>
       <c r="AC95" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AD95" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AE95" s="19" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AF95" s="19" t="s">
         <v>48</v>
@@ -11609,22 +11609,22 @@
     </row>
     <row r="96" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="C96" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="D96" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="E96" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="D96" s="16" t="s">
+      <c r="F96" s="16" t="s">
         <v>532</v>
-      </c>
-      <c r="E96" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>534</v>
       </c>
       <c r="G96" s="16" t="s">
         <v>39</v>
@@ -11633,7 +11633,7 @@
         <v>40</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="J96" s="16">
         <v>1200000</v>
@@ -11645,7 +11645,7 @@
         <v>25000</v>
       </c>
       <c r="M96" s="16" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N96" s="16" t="s">
         <v>43</v>
@@ -11675,7 +11675,7 @@
         <v>1000</v>
       </c>
       <c r="W96" s="16" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="X96" s="16"/>
       <c r="Y96" s="16"/>
@@ -11686,10 +11686,10 @@
         <v>70</v>
       </c>
       <c r="AD96" s="19" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AE96" s="19" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AF96" s="19" t="s">
         <v>48</v>
@@ -11706,22 +11706,22 @@
     </row>
     <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B97" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D97" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="E97" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="F97" s="16" t="s">
         <v>540</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="E97" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="F97" s="16" t="s">
-        <v>542</v>
       </c>
       <c r="G97" s="16" t="s">
         <v>39</v>
@@ -11730,7 +11730,7 @@
         <v>40</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J97" s="16">
         <v>500000</v>
@@ -11742,7 +11742,7 @@
         <v>10000</v>
       </c>
       <c r="M97" s="16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N97" s="16" t="s">
         <v>43</v>
@@ -11772,7 +11772,7 @@
         <v>500</v>
       </c>
       <c r="W97" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="X97" s="16"/>
       <c r="Y97" s="16"/>
@@ -11783,10 +11783,10 @@
         <v>70</v>
       </c>
       <c r="AD97" s="19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AE97" s="19" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AF97" s="19" t="s">
         <v>48</v>
@@ -11803,22 +11803,22 @@
     </row>
     <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B98" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D98" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="E98" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="F98" s="16" t="s">
         <v>548</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>549</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>550</v>
       </c>
       <c r="G98" s="16" t="s">
         <v>39</v>
@@ -11827,19 +11827,19 @@
         <v>40</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="J98" s="16">
         <v>280000</v>
       </c>
       <c r="K98" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L98" s="16">
         <v>8000</v>
       </c>
       <c r="M98" s="16" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N98" s="16" t="s">
         <v>43</v>
@@ -11854,7 +11854,7 @@
         <v>20000</v>
       </c>
       <c r="R98" s="16" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="S98" s="16"/>
       <c r="T98" s="16"/>
@@ -11870,10 +11870,10 @@
         <v>70</v>
       </c>
       <c r="AD98" s="19" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AE98" s="19" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AF98" s="19" t="s">
         <v>233</v>
@@ -11890,22 +11890,22 @@
     </row>
     <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B99" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="D99" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="E99" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="F99" s="16" t="s">
         <v>557</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="E99" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="F99" s="16" t="s">
-        <v>559</v>
       </c>
       <c r="G99" s="16" t="s">
         <v>39</v>
@@ -11914,7 +11914,7 @@
         <v>40</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J99" s="16">
         <v>1100000</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="W99" s="16" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="X99" s="16"/>
       <c r="Y99" s="16"/>
@@ -11967,10 +11967,10 @@
         <v>70</v>
       </c>
       <c r="AD99" s="19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AE99" s="19" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AF99" s="19" t="s">
         <v>48</v>
@@ -11987,22 +11987,22 @@
     </row>
     <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C100" s="16" t="s">
         <v>563</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="D100" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="E100" s="16" t="s">
         <v>565</v>
       </c>
-      <c r="D100" s="16" t="s">
+      <c r="F100" s="16" t="s">
         <v>566</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>567</v>
-      </c>
-      <c r="F100" s="16" t="s">
-        <v>568</v>
       </c>
       <c r="G100" s="16" t="s">
         <v>39</v>
@@ -12011,7 +12011,7 @@
         <v>132</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J100" s="16">
         <v>650000</v>
@@ -12023,7 +12023,7 @@
         <v>12000</v>
       </c>
       <c r="M100" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N100" s="16" t="s">
         <v>43</v>
@@ -12038,7 +12038,7 @@
         <v>60000</v>
       </c>
       <c r="R100" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S100" s="16">
         <v>60000</v>
@@ -12053,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="W100" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X100" s="16"/>
       <c r="Y100" s="16"/>
@@ -12064,10 +12064,10 @@
         <v>70</v>
       </c>
       <c r="AD100" s="19" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AE100" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AF100" s="19" t="s">
         <v>233</v>
@@ -12084,22 +12084,22 @@
     </row>
     <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B101" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="D101" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="C101" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="D101" s="16" t="s">
+      <c r="E101" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="F101" s="16" t="s">
         <v>566</v>
-      </c>
-      <c r="E101" s="16" t="s">
-        <v>576</v>
-      </c>
-      <c r="F101" s="16" t="s">
-        <v>568</v>
       </c>
       <c r="G101" s="16" t="s">
         <v>39</v>
@@ -12108,7 +12108,7 @@
         <v>132</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J101" s="16">
         <v>650000</v>
@@ -12120,7 +12120,7 @@
         <v>12000</v>
       </c>
       <c r="M101" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N101" s="16" t="s">
         <v>43</v>
@@ -12135,7 +12135,7 @@
         <v>60000</v>
       </c>
       <c r="R101" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S101" s="16">
         <v>60000</v>
@@ -12150,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="W101" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X101" s="16"/>
       <c r="Y101" s="16"/>
@@ -12158,13 +12158,13 @@
       <c r="AA101" s="16"/>
       <c r="AB101" s="19"/>
       <c r="AC101" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AD101" s="19" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AE101" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AF101" s="19" t="s">
         <v>233</v>
@@ -12181,22 +12181,22 @@
     </row>
     <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B102" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C102" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="D102" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="C102" s="16" t="s">
-        <v>578</v>
-      </c>
-      <c r="D102" s="16" t="s">
+      <c r="E102" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="F102" s="16" t="s">
         <v>566</v>
-      </c>
-      <c r="E102" s="16" t="s">
-        <v>579</v>
-      </c>
-      <c r="F102" s="16" t="s">
-        <v>568</v>
       </c>
       <c r="G102" s="16" t="s">
         <v>39</v>
@@ -12205,7 +12205,7 @@
         <v>132</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J102" s="16">
         <v>650000</v>
@@ -12217,7 +12217,7 @@
         <v>12000</v>
       </c>
       <c r="M102" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N102" s="16" t="s">
         <v>43</v>
@@ -12232,7 +12232,7 @@
         <v>60000</v>
       </c>
       <c r="R102" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S102" s="16">
         <v>60000</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="W102" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X102" s="16">
         <v>1000</v>
@@ -12257,17 +12257,17 @@
         <v>260</v>
       </c>
       <c r="AA102" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AB102" s="19"/>
       <c r="AC102" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD102" s="19" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AE102" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AF102" s="19" t="s">
         <v>48</v>
@@ -12284,22 +12284,22 @@
     </row>
     <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B103" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>580</v>
+      </c>
+      <c r="D103" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="C103" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="D103" s="16" t="s">
+      <c r="E103" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="F103" s="16" t="s">
         <v>566</v>
-      </c>
-      <c r="E103" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="F103" s="16" t="s">
-        <v>568</v>
       </c>
       <c r="G103" s="16" t="s">
         <v>39</v>
@@ -12308,7 +12308,7 @@
         <v>132</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J103" s="16">
         <v>650000</v>
@@ -12320,7 +12320,7 @@
         <v>12000</v>
       </c>
       <c r="M103" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N103" s="16" t="s">
         <v>43</v>
@@ -12335,7 +12335,7 @@
         <v>60000</v>
       </c>
       <c r="R103" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S103" s="16">
         <v>60000</v>
@@ -12350,7 +12350,7 @@
         <v>0</v>
       </c>
       <c r="W103" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X103" s="16"/>
       <c r="Y103" s="16"/>
@@ -12358,16 +12358,16 @@
       <c r="AA103" s="16"/>
       <c r="AB103" s="19"/>
       <c r="AC103" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="AD103" s="19" t="s">
+        <v>869</v>
+      </c>
+      <c r="AE103" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="AD103" s="19" t="s">
+      <c r="AF103" s="19" t="s">
         <v>871</v>
-      </c>
-      <c r="AE103" s="19" t="s">
-        <v>872</v>
-      </c>
-      <c r="AF103" s="19" t="s">
-        <v>873</v>
       </c>
       <c r="AG103" s="20" t="s">
         <v>49</v>
@@ -12381,22 +12381,22 @@
     </row>
     <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B104" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="D104" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="C104" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="D104" s="16" t="s">
+      <c r="E104" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="F104" s="16" t="s">
         <v>566</v>
-      </c>
-      <c r="E104" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="F104" s="16" t="s">
-        <v>568</v>
       </c>
       <c r="G104" s="16" t="s">
         <v>39</v>
@@ -12405,7 +12405,7 @@
         <v>132</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J104" s="16">
         <v>650000</v>
@@ -12417,7 +12417,7 @@
         <v>12000</v>
       </c>
       <c r="M104" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N104" s="16" t="s">
         <v>43</v>
@@ -12432,7 +12432,7 @@
         <v>60000</v>
       </c>
       <c r="R104" s="16" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S104" s="16">
         <v>60000</v>
@@ -12447,7 +12447,7 @@
         <v>0</v>
       </c>
       <c r="W104" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X104" s="16"/>
       <c r="Y104" s="16"/>
@@ -12455,16 +12455,16 @@
       <c r="AA104" s="16"/>
       <c r="AB104" s="19"/>
       <c r="AC104" s="19" t="s">
+        <v>868</v>
+      </c>
+      <c r="AD104" s="19" t="s">
+        <v>869</v>
+      </c>
+      <c r="AE104" s="19" t="s">
         <v>870</v>
       </c>
-      <c r="AD104" s="19" t="s">
+      <c r="AF104" s="19" t="s">
         <v>871</v>
-      </c>
-      <c r="AE104" s="19" t="s">
-        <v>872</v>
-      </c>
-      <c r="AF104" s="19" t="s">
-        <v>873</v>
       </c>
       <c r="AG104" s="20" t="s">
         <v>49</v>
@@ -12478,22 +12478,22 @@
     </row>
     <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="C105" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="D105" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="E105" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="D105" s="16" t="s">
+      <c r="F105" s="16" t="s">
         <v>589</v>
-      </c>
-      <c r="E105" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F105" s="16" t="s">
-        <v>591</v>
       </c>
       <c r="G105" s="16" t="s">
         <v>39</v>
@@ -12502,19 +12502,19 @@
         <v>40</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J105" s="16">
         <v>900000</v>
       </c>
       <c r="K105" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L105" s="16">
         <v>15000</v>
       </c>
       <c r="M105" s="16" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N105" s="16" t="s">
         <v>43</v>
@@ -12544,7 +12544,7 @@
         <v>1000</v>
       </c>
       <c r="W105" s="16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="X105" s="16"/>
       <c r="Y105" s="16"/>
@@ -12552,16 +12552,16 @@
       <c r="AA105" s="16"/>
       <c r="AB105" s="19"/>
       <c r="AC105" s="19" t="s">
+        <v>872</v>
+      </c>
+      <c r="AD105" s="19" t="s">
+        <v>873</v>
+      </c>
+      <c r="AE105" s="19" t="s">
         <v>874</v>
       </c>
-      <c r="AD105" s="19" t="s">
-        <v>875</v>
-      </c>
-      <c r="AE105" s="19" t="s">
-        <v>876</v>
-      </c>
       <c r="AF105" s="19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AG105" s="20" t="s">
         <v>49</v>
@@ -12575,22 +12575,22 @@
     </row>
     <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B106" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="D106" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="C106" s="16" t="s">
-        <v>595</v>
-      </c>
-      <c r="D106" s="16" t="s">
+      <c r="E106" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="F106" s="16" t="s">
         <v>589</v>
-      </c>
-      <c r="E106" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="F106" s="16" t="s">
-        <v>591</v>
       </c>
       <c r="G106" s="16" t="s">
         <v>39</v>
@@ -12599,19 +12599,19 @@
         <v>40</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J106" s="16">
         <v>900000</v>
       </c>
       <c r="K106" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L106" s="16">
         <v>15000</v>
       </c>
       <c r="M106" s="16" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N106" s="16" t="s">
         <v>43</v>
@@ -12641,7 +12641,7 @@
         <v>1000</v>
       </c>
       <c r="W106" s="16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="X106" s="16"/>
       <c r="Y106" s="16"/>
@@ -12649,16 +12649,16 @@
       <c r="AA106" s="16"/>
       <c r="AB106" s="19"/>
       <c r="AC106" s="19" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="AD106" s="19" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="AE106" s="19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="AF106" s="19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AG106" s="20" t="s">
         <v>49</v>
@@ -12672,22 +12672,22 @@
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B107" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="D107" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="C107" s="16" t="s">
-        <v>597</v>
-      </c>
-      <c r="D107" s="16" t="s">
+      <c r="E107" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="F107" s="16" t="s">
         <v>589</v>
-      </c>
-      <c r="E107" s="16" t="s">
-        <v>598</v>
-      </c>
-      <c r="F107" s="16" t="s">
-        <v>591</v>
       </c>
       <c r="G107" s="16" t="s">
         <v>39</v>
@@ -12696,19 +12696,19 @@
         <v>40</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="J107" s="16">
         <v>900000</v>
       </c>
       <c r="K107" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L107" s="16">
         <v>15000</v>
       </c>
       <c r="M107" s="16" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="N107" s="16" t="s">
         <v>43</v>
@@ -12738,7 +12738,7 @@
         <v>1000</v>
       </c>
       <c r="W107" s="16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="X107" s="16"/>
       <c r="Y107" s="16"/>
@@ -12746,16 +12746,16 @@
       <c r="AA107" s="16"/>
       <c r="AB107" s="19"/>
       <c r="AC107" s="19" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="AD107" s="19" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="AE107" s="19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="AF107" s="19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AG107" s="20" t="s">
         <v>49</v>
@@ -12769,22 +12769,22 @@
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C108" s="16" t="s">
         <v>599</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="D108" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="E108" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D108" s="16" t="s">
+      <c r="F108" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="E108" s="16" t="s">
-        <v>603</v>
-      </c>
-      <c r="F108" s="16" t="s">
-        <v>604</v>
       </c>
       <c r="G108" s="16" t="s">
         <v>39</v>
@@ -12793,7 +12793,7 @@
         <v>40</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J108" s="16">
         <v>700000</v>
@@ -12805,7 +12805,7 @@
         <v>18000</v>
       </c>
       <c r="M108" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N108" s="16" t="s">
         <v>43</v>
@@ -12835,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="W108" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X108" s="16">
         <v>0</v>
@@ -12845,17 +12845,17 @@
         <v>250</v>
       </c>
       <c r="AA108" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AB108" s="19"/>
       <c r="AC108" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD108" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AE108" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AF108" s="19" t="s">
         <v>48</v>
@@ -12872,22 +12872,22 @@
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B109" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="D109" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C109" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="D109" s="16" t="s">
+      <c r="E109" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="F109" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="E109" s="16" t="s">
-        <v>611</v>
-      </c>
-      <c r="F109" s="16" t="s">
-        <v>604</v>
       </c>
       <c r="G109" s="16" t="s">
         <v>39</v>
@@ -12896,7 +12896,7 @@
         <v>40</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J109" s="16">
         <v>700000</v>
@@ -12908,7 +12908,7 @@
         <v>18000</v>
       </c>
       <c r="M109" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N109" s="16" t="s">
         <v>43</v>
@@ -12938,7 +12938,7 @@
         <v>0</v>
       </c>
       <c r="W109" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X109" s="16">
         <v>-500</v>
@@ -12948,17 +12948,17 @@
         <v>250</v>
       </c>
       <c r="AA109" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AB109" s="19"/>
       <c r="AC109" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD109" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AE109" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AF109" s="19" t="s">
         <v>48</v>
@@ -12975,22 +12975,22 @@
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B110" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="D110" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="E110" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="F110" s="16" t="s">
         <v>612</v>
-      </c>
-      <c r="D110" s="16" t="s">
-        <v>602</v>
-      </c>
-      <c r="E110" s="16" t="s">
-        <v>613</v>
-      </c>
-      <c r="F110" s="16" t="s">
-        <v>614</v>
       </c>
       <c r="G110" s="16" t="s">
         <v>39</v>
@@ -12999,7 +12999,7 @@
         <v>40</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J110" s="16">
         <v>850000</v>
@@ -13011,7 +13011,7 @@
         <v>22000</v>
       </c>
       <c r="M110" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="N110" s="16" t="s">
         <v>43</v>
@@ -13041,30 +13041,30 @@
         <v>3000</v>
       </c>
       <c r="W110" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X110" s="16">
         <v>5000</v>
       </c>
       <c r="Y110" s="16"/>
       <c r="Z110" s="16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AA110" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AB110" s="19"/>
       <c r="AC110" s="19" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AD110" s="19" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="AE110" s="19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="AF110" s="19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AG110" s="20" t="s">
         <v>49</v>
@@ -13078,22 +13078,22 @@
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B111" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="D111" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C111" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="D111" s="16" t="s">
-        <v>602</v>
-      </c>
       <c r="E111" s="16" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G111" s="16" t="s">
         <v>39</v>
@@ -13102,7 +13102,7 @@
         <v>40</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J111" s="16">
         <v>850000</v>
@@ -13114,7 +13114,7 @@
         <v>22000</v>
       </c>
       <c r="M111" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="N111" s="16" t="s">
         <v>43</v>
@@ -13144,30 +13144,30 @@
         <v>3000</v>
       </c>
       <c r="W111" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X111" s="16">
         <v>2500</v>
       </c>
       <c r="Y111" s="16"/>
       <c r="Z111" s="16" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AA111" s="16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AB111" s="19"/>
       <c r="AC111" s="19" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AD111" s="19" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="AE111" s="19" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="AF111" s="19" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="AG111" s="20" t="s">
         <v>49</v>
@@ -13181,22 +13181,22 @@
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B112" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="D112" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C112" s="16" t="s">
+      <c r="E112" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="F112" s="16" t="s">
         <v>620</v>
-      </c>
-      <c r="D112" s="16" t="s">
-        <v>602</v>
-      </c>
-      <c r="E112" s="16" t="s">
-        <v>621</v>
-      </c>
-      <c r="F112" s="16" t="s">
-        <v>622</v>
       </c>
       <c r="G112" s="16" t="s">
         <v>39</v>
@@ -13205,19 +13205,19 @@
         <v>40</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="J112" s="16">
         <v>1500000</v>
       </c>
       <c r="K112" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L112" s="16">
         <v>35000</v>
       </c>
       <c r="M112" s="16" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="N112" s="16" t="s">
         <v>43</v>
@@ -13247,27 +13247,27 @@
         <v>0</v>
       </c>
       <c r="W112" s="16" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="X112" s="16">
         <v>170000</v>
       </c>
       <c r="Y112" s="16"/>
       <c r="Z112" s="16" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AA112" s="16" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AB112" s="19"/>
       <c r="AC112" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD112" s="19" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AE112" s="19" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AF112" s="19" t="s">
         <v>48</v>
@@ -13284,22 +13284,22 @@
     </row>
     <row r="113" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A113" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B113" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="D113" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C113" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="D113" s="16" t="s">
+      <c r="E113" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F113" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="E113" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="F113" s="16" t="s">
-        <v>604</v>
       </c>
       <c r="G113" s="16" t="s">
         <v>39</v>
@@ -13308,7 +13308,7 @@
         <v>40</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J113" s="16">
         <v>700000</v>
@@ -13320,7 +13320,7 @@
         <v>18000</v>
       </c>
       <c r="M113" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N113" s="16" t="s">
         <v>43</v>
@@ -13350,27 +13350,27 @@
         <v>0</v>
       </c>
       <c r="W113" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X113" s="16">
         <v>3000</v>
       </c>
       <c r="Y113" s="16"/>
       <c r="Z113" s="16" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AA113" s="16" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AB113" s="19"/>
       <c r="AC113" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD113" s="19" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AE113" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AF113" s="19" t="s">
         <v>233</v>
@@ -13387,22 +13387,22 @@
     </row>
     <row r="114" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B114" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="D114" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="C114" s="16" t="s">
-        <v>636</v>
-      </c>
-      <c r="D114" s="16" t="s">
+      <c r="E114" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="F114" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="E114" s="16" t="s">
-        <v>637</v>
-      </c>
-      <c r="F114" s="16" t="s">
-        <v>604</v>
       </c>
       <c r="G114" s="16" t="s">
         <v>39</v>
@@ -13411,7 +13411,7 @@
         <v>40</v>
       </c>
       <c r="I114" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J114" s="16">
         <v>700000</v>
@@ -13423,7 +13423,7 @@
         <v>18000</v>
       </c>
       <c r="M114" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N114" s="16" t="s">
         <v>43</v>
@@ -13453,27 +13453,27 @@
         <v>500</v>
       </c>
       <c r="W114" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="X114" s="16">
         <v>500</v>
       </c>
       <c r="Y114" s="16"/>
       <c r="Z114" s="16" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AA114" s="16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AB114" s="19"/>
       <c r="AC114" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD114" s="19" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AE114" s="19" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AF114" s="19" t="s">
         <v>233</v>
@@ -13490,22 +13490,22 @@
     </row>
     <row r="115" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
+        <v>640</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C115" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="D115" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="C115" s="16" t="s">
+      <c r="E115" s="16" t="s">
         <v>644</v>
       </c>
-      <c r="D115" s="16" t="s">
+      <c r="F115" s="16" t="s">
         <v>645</v>
-      </c>
-      <c r="E115" s="16" t="s">
-        <v>646</v>
-      </c>
-      <c r="F115" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="G115" s="16" t="s">
         <v>39</v>
@@ -13514,7 +13514,7 @@
         <v>40</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J115" s="16">
         <v>750000</v>
@@ -13526,7 +13526,7 @@
         <v>16000</v>
       </c>
       <c r="M115" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N115" s="16" t="s">
         <v>43</v>
@@ -13556,7 +13556,7 @@
         <v>3000</v>
       </c>
       <c r="W115" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="X115" s="16">
         <v>35000</v>
@@ -13565,20 +13565,20 @@
         <v>90000</v>
       </c>
       <c r="Z115" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AA115" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AB115" s="19"/>
       <c r="AC115" s="19" t="s">
         <v>279</v>
       </c>
       <c r="AD115" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AE115" s="19" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AF115" s="19" t="s">
         <v>48</v>
@@ -13595,22 +13595,22 @@
     </row>
     <row r="116" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B116" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D116" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="C116" s="16" t="s">
-        <v>652</v>
-      </c>
-      <c r="D116" s="16" t="s">
+      <c r="E116" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="F116" s="16" t="s">
         <v>645</v>
-      </c>
-      <c r="E116" s="16" t="s">
-        <v>653</v>
-      </c>
-      <c r="F116" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="G116" s="16" t="s">
         <v>39</v>
@@ -13619,7 +13619,7 @@
         <v>40</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J116" s="16">
         <v>750000</v>
@@ -13631,7 +13631,7 @@
         <v>16000</v>
       </c>
       <c r="M116" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N116" s="16" t="s">
         <v>43</v>
@@ -13661,7 +13661,7 @@
         <v>3000</v>
       </c>
       <c r="W116" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="X116" s="16">
         <v>1000</v>
@@ -13670,20 +13670,20 @@
         <v>500</v>
       </c>
       <c r="Z116" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AA116" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AB116" s="19"/>
       <c r="AC116" s="19" t="s">
         <v>279</v>
       </c>
       <c r="AD116" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AE116" s="19" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AF116" s="19" t="s">
         <v>48</v>
@@ -13700,22 +13700,22 @@
     </row>
     <row r="117" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B117" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="D117" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="C117" s="16" t="s">
-        <v>654</v>
-      </c>
-      <c r="D117" s="16" t="s">
+      <c r="E117" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="F117" s="16" t="s">
         <v>645</v>
-      </c>
-      <c r="E117" s="16" t="s">
-        <v>655</v>
-      </c>
-      <c r="F117" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="G117" s="16" t="s">
         <v>39</v>
@@ -13724,7 +13724,7 @@
         <v>40</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J117" s="16">
         <v>750000</v>
@@ -13736,7 +13736,7 @@
         <v>16000</v>
       </c>
       <c r="M117" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N117" s="16" t="s">
         <v>43</v>
@@ -13766,7 +13766,7 @@
         <v>3000</v>
       </c>
       <c r="W117" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="X117" s="16">
         <v>5000</v>
@@ -13775,20 +13775,20 @@
         <v>2000</v>
       </c>
       <c r="Z117" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AA117" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AB117" s="19"/>
       <c r="AC117" s="19" t="s">
         <v>279</v>
       </c>
       <c r="AD117" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AE117" s="19" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AF117" s="19" t="s">
         <v>48</v>
@@ -13805,22 +13805,22 @@
     </row>
     <row r="118" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B118" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="D118" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="C118" s="16" t="s">
-        <v>656</v>
-      </c>
-      <c r="D118" s="16" t="s">
+      <c r="E118" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="F118" s="16" t="s">
         <v>645</v>
-      </c>
-      <c r="E118" s="16" t="s">
-        <v>657</v>
-      </c>
-      <c r="F118" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="G118" s="16" t="s">
         <v>39</v>
@@ -13829,7 +13829,7 @@
         <v>40</v>
       </c>
       <c r="I118" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J118" s="16">
         <v>750000</v>
@@ -13841,7 +13841,7 @@
         <v>16000</v>
       </c>
       <c r="M118" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N118" s="16" t="s">
         <v>43</v>
@@ -13871,7 +13871,7 @@
         <v>3000</v>
       </c>
       <c r="W118" s="16" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="X118" s="16">
         <v>3000</v>
@@ -13880,20 +13880,20 @@
         <v>1000</v>
       </c>
       <c r="Z118" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AA118" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AB118" s="19"/>
       <c r="AC118" s="19" t="s">
         <v>279</v>
       </c>
       <c r="AD118" s="19" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AE118" s="19" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AF118" s="19" t="s">
         <v>48</v>
@@ -13910,22 +13910,22 @@
     </row>
     <row r="119" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B119" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D119" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="C119" s="16" t="s">
-        <v>658</v>
-      </c>
-      <c r="D119" s="16" t="s">
+      <c r="E119" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="F119" s="16" t="s">
         <v>645</v>
-      </c>
-      <c r="E119" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="F119" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="G119" s="16" t="s">
         <v>39</v>
@@ -13934,7 +13934,7 @@
         <v>40</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="J119" s="16">
         <v>750000</v>
@@ -13946,7 +13946,7 @@
         <v>16000</v>
       </c>
       <c r="M119" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="N119" s="16" t="s">
         <v>43</v>
@@ -13976,26 +13976,26 @@
         <v>0</v>
       </c>
       <c r="W119" s="16" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="X119" s="16"/>
       <c r="Y119" s="16"/>
       <c r="Z119" s="16"/>
       <c r="AA119" s="16"/>
       <c r="AB119" s="19" t="s">
+        <v>881</v>
+      </c>
+      <c r="AC119" s="19" t="s">
+        <v>882</v>
+      </c>
+      <c r="AD119" s="19" t="s">
         <v>883</v>
       </c>
-      <c r="AC119" s="19" t="s">
+      <c r="AE119" s="19" t="s">
         <v>884</v>
       </c>
-      <c r="AD119" s="19" t="s">
+      <c r="AF119" s="19" t="s">
         <v>885</v>
-      </c>
-      <c r="AE119" s="19" t="s">
-        <v>886</v>
-      </c>
-      <c r="AF119" s="19" t="s">
-        <v>887</v>
       </c>
       <c r="AG119" s="20" t="s">
         <v>49</v>
@@ -14009,22 +14009,22 @@
     </row>
     <row r="120" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C120" s="16" t="s">
         <v>661</v>
       </c>
-      <c r="B120" s="16" t="s">
+      <c r="D120" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C120" s="16" t="s">
+      <c r="E120" s="16" t="s">
         <v>663</v>
       </c>
-      <c r="D120" s="16" t="s">
+      <c r="F120" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>665</v>
-      </c>
-      <c r="F120" s="16" t="s">
-        <v>666</v>
       </c>
       <c r="G120" s="16" t="s">
         <v>39</v>
@@ -14033,7 +14033,7 @@
         <v>40</v>
       </c>
       <c r="I120" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J120" s="16">
         <v>900000</v>
@@ -14045,7 +14045,7 @@
         <v>14000</v>
       </c>
       <c r="M120" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N120" s="16" t="s">
         <v>43</v>
@@ -14075,7 +14075,7 @@
         <v>3000</v>
       </c>
       <c r="W120" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X120" s="16"/>
       <c r="Y120" s="16"/>
@@ -14083,13 +14083,13 @@
       <c r="AA120" s="16"/>
       <c r="AB120" s="19"/>
       <c r="AC120" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD120" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AE120" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AF120" s="19" t="s">
         <v>48</v>
@@ -14106,22 +14106,22 @@
     </row>
     <row r="121" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B121" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C121" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="D121" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C121" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="D121" s="16" t="s">
+      <c r="E121" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="F121" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="E121" s="16" t="s">
-        <v>670</v>
-      </c>
-      <c r="F121" s="16" t="s">
-        <v>666</v>
       </c>
       <c r="G121" s="16" t="s">
         <v>39</v>
@@ -14130,7 +14130,7 @@
         <v>40</v>
       </c>
       <c r="I121" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J121" s="16">
         <v>900000</v>
@@ -14142,7 +14142,7 @@
         <v>14000</v>
       </c>
       <c r="M121" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N121" s="16" t="s">
         <v>43</v>
@@ -14172,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="W121" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X121" s="16"/>
       <c r="Y121" s="16"/>
@@ -14180,13 +14180,13 @@
       <c r="AA121" s="16"/>
       <c r="AB121" s="19"/>
       <c r="AC121" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD121" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AE121" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AF121" s="19" t="s">
         <v>48</v>
@@ -14203,22 +14203,22 @@
     </row>
     <row r="122" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B122" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="D122" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C122" s="16" t="s">
-        <v>671</v>
-      </c>
-      <c r="D122" s="16" t="s">
+      <c r="E122" s="16" t="s">
+        <v>670</v>
+      </c>
+      <c r="F122" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>672</v>
-      </c>
-      <c r="F122" s="16" t="s">
-        <v>666</v>
       </c>
       <c r="G122" s="16" t="s">
         <v>39</v>
@@ -14227,7 +14227,7 @@
         <v>40</v>
       </c>
       <c r="I122" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J122" s="16">
         <v>900000</v>
@@ -14239,7 +14239,7 @@
         <v>14000</v>
       </c>
       <c r="M122" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N122" s="16" t="s">
         <v>43</v>
@@ -14269,7 +14269,7 @@
         <v>3000</v>
       </c>
       <c r="W122" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X122" s="16"/>
       <c r="Y122" s="16"/>
@@ -14277,13 +14277,13 @@
       <c r="AA122" s="16"/>
       <c r="AB122" s="19"/>
       <c r="AC122" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD122" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AE122" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AF122" s="19" t="s">
         <v>48</v>
@@ -14300,22 +14300,22 @@
     </row>
     <row r="123" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B123" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C123" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="D123" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C123" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="D123" s="16" t="s">
+      <c r="E123" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="F123" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="E123" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="F123" s="16" t="s">
-        <v>666</v>
       </c>
       <c r="G123" s="16" t="s">
         <v>39</v>
@@ -14324,7 +14324,7 @@
         <v>40</v>
       </c>
       <c r="I123" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J123" s="16">
         <v>900000</v>
@@ -14336,7 +14336,7 @@
         <v>14000</v>
       </c>
       <c r="M123" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N123" s="16" t="s">
         <v>43</v>
@@ -14366,7 +14366,7 @@
         <v>3000</v>
       </c>
       <c r="W123" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X123" s="16"/>
       <c r="Y123" s="16"/>
@@ -14374,13 +14374,13 @@
       <c r="AA123" s="16"/>
       <c r="AB123" s="19"/>
       <c r="AC123" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD123" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AE123" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AF123" s="19" t="s">
         <v>48</v>
@@ -14397,22 +14397,22 @@
     </row>
     <row r="124" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B124" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="D124" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C124" s="16" t="s">
-        <v>675</v>
-      </c>
-      <c r="D124" s="16" t="s">
+      <c r="E124" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="F124" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="E124" s="16" t="s">
-        <v>676</v>
-      </c>
-      <c r="F124" s="16" t="s">
-        <v>666</v>
       </c>
       <c r="G124" s="16" t="s">
         <v>39</v>
@@ -14421,7 +14421,7 @@
         <v>40</v>
       </c>
       <c r="I124" s="17" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="J124" s="16">
         <v>900000</v>
@@ -14433,7 +14433,7 @@
         <v>14000</v>
       </c>
       <c r="M124" s="16" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N124" s="16" t="s">
         <v>43</v>
@@ -14463,7 +14463,7 @@
         <v>11000</v>
       </c>
       <c r="W124" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="X124" s="16"/>
       <c r="Y124" s="16"/>
@@ -14471,13 +14471,13 @@
       <c r="AA124" s="16"/>
       <c r="AB124" s="19"/>
       <c r="AC124" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD124" s="19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AE124" s="19" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AF124" s="19" t="s">
         <v>48</v>
@@ -14494,22 +14494,22 @@
     </row>
     <row r="125" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C125" s="16" t="s">
         <v>677</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="D125" s="16" t="s">
         <v>678</v>
       </c>
-      <c r="C125" s="16" t="s">
+      <c r="E125" s="16" t="s">
         <v>679</v>
       </c>
-      <c r="D125" s="16" t="s">
+      <c r="F125" s="16" t="s">
         <v>680</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>681</v>
-      </c>
-      <c r="F125" s="16" t="s">
-        <v>682</v>
       </c>
       <c r="G125" s="16" t="s">
         <v>39</v>
@@ -14518,7 +14518,7 @@
         <v>40</v>
       </c>
       <c r="I125" s="17" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J125" s="16">
         <v>650000</v>
@@ -14530,7 +14530,7 @@
         <v>9000</v>
       </c>
       <c r="M125" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N125" s="16" t="s">
         <v>43</v>
@@ -14560,7 +14560,7 @@
         <v>500</v>
       </c>
       <c r="W125" s="16" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="X125" s="16"/>
       <c r="Y125" s="16"/>
@@ -14568,13 +14568,13 @@
       <c r="AA125" s="16"/>
       <c r="AB125" s="19"/>
       <c r="AC125" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AD125" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AE125" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="AF125" s="19" t="s">
         <v>48</v>
@@ -14591,22 +14591,22 @@
     </row>
     <row r="126" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B126" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="D126" s="16" t="s">
         <v>678</v>
       </c>
-      <c r="C126" s="16" t="s">
-        <v>688</v>
-      </c>
-      <c r="D126" s="16" t="s">
+      <c r="E126" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="F126" s="16" t="s">
         <v>680</v>
-      </c>
-      <c r="E126" s="16" t="s">
-        <v>689</v>
-      </c>
-      <c r="F126" s="16" t="s">
-        <v>682</v>
       </c>
       <c r="G126" s="16" t="s">
         <v>39</v>
@@ -14615,7 +14615,7 @@
         <v>40</v>
       </c>
       <c r="I126" s="17" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J126" s="16">
         <v>650000</v>
@@ -14627,7 +14627,7 @@
         <v>9000</v>
       </c>
       <c r="M126" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N126" s="16" t="s">
         <v>43</v>
@@ -14657,7 +14657,7 @@
         <v>500</v>
       </c>
       <c r="W126" s="16" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="X126" s="16"/>
       <c r="Y126" s="16"/>
@@ -14665,13 +14665,13 @@
       <c r="AA126" s="16"/>
       <c r="AB126" s="19"/>
       <c r="AC126" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AD126" s="19" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AE126" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AF126" s="19" t="s">
         <v>48</v>
@@ -14688,31 +14688,31 @@
     </row>
     <row r="127" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B127" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="D127" s="16" t="s">
         <v>678</v>
       </c>
-      <c r="C127" s="16" t="s">
-        <v>691</v>
-      </c>
-      <c r="D127" s="16" t="s">
+      <c r="E127" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="F127" s="16" t="s">
         <v>680</v>
       </c>
-      <c r="E127" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="F127" s="16" t="s">
-        <v>682</v>
-      </c>
       <c r="G127" s="16" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H127" s="16" t="s">
         <v>40</v>
       </c>
       <c r="I127" s="17" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J127" s="16">
         <v>650000</v>
@@ -14724,7 +14724,7 @@
         <v>9000</v>
       </c>
       <c r="M127" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N127" s="16" t="s">
         <v>43</v>
@@ -14754,27 +14754,27 @@
         <v>500</v>
       </c>
       <c r="W127" s="16" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="X127" s="16">
         <v>1200</v>
       </c>
       <c r="Y127" s="16"/>
       <c r="Z127" s="16" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AA127" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="AB127" s="19"/>
       <c r="AC127" s="19" t="s">
         <v>252</v>
       </c>
       <c r="AD127" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AE127" s="19" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AF127" s="19" t="s">
         <v>48</v>
@@ -14791,22 +14791,22 @@
     </row>
     <row r="128" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B128" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="D128" s="16" t="s">
         <v>678</v>
       </c>
-      <c r="C128" s="16" t="s">
-        <v>696</v>
-      </c>
-      <c r="D128" s="16" t="s">
+      <c r="E128" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="F128" s="16" t="s">
         <v>680</v>
-      </c>
-      <c r="E128" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="F128" s="16" t="s">
-        <v>682</v>
       </c>
       <c r="G128" s="16" t="s">
         <v>39</v>
@@ -14815,7 +14815,7 @@
         <v>40</v>
       </c>
       <c r="I128" s="17" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J128" s="16">
         <v>650000</v>
@@ -14827,7 +14827,7 @@
         <v>9000</v>
       </c>
       <c r="M128" s="16" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="N128" s="16" t="s">
         <v>43</v>
@@ -14856,10 +14856,10 @@
         <v>70</v>
       </c>
       <c r="AD128" s="19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AE128" s="19" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="AF128" s="19" t="s">
         <v>233</v>
@@ -14876,19 +14876,19 @@
     </row>
     <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="C129" s="16" t="s">
         <v>700</v>
       </c>
-      <c r="B129" s="16" t="s">
+      <c r="D129" s="16" t="s">
         <v>701</v>
       </c>
-      <c r="C129" s="16" t="s">
+      <c r="E129" s="16" t="s">
         <v>702</v>
-      </c>
-      <c r="D129" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="E129" s="16" t="s">
-        <v>704</v>
       </c>
       <c r="F129" s="16" t="s">
         <v>123</v>
@@ -14912,7 +14912,7 @@
         <v>5000</v>
       </c>
       <c r="M129" s="16" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="N129" s="16" t="s">
         <v>43</v>
@@ -14941,10 +14941,10 @@
         <v>70</v>
       </c>
       <c r="AD129" s="19" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AE129" s="19" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AF129" s="19" t="s">
         <v>48</v>
@@ -14961,19 +14961,19 @@
     </row>
     <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B130" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="D130" s="16" t="s">
         <v>701</v>
       </c>
-      <c r="C130" s="16" t="s">
-        <v>708</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>703</v>
-      </c>
       <c r="E130" s="16" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F130" s="16" t="s">
         <v>123</v>
@@ -14985,7 +14985,7 @@
         <v>40</v>
       </c>
       <c r="I130" s="17" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="J130" s="16">
         <v>250000</v>
@@ -14997,7 +14997,7 @@
         <v>4000</v>
       </c>
       <c r="M130" s="16" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="N130" s="16" t="s">
         <v>43</v>
@@ -15009,7 +15009,7 @@
         <v>44</v>
       </c>
       <c r="Q130" s="16" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="R130" s="16"/>
       <c r="S130" s="16"/>
@@ -15026,10 +15026,10 @@
         <v>70</v>
       </c>
       <c r="AD130" s="19" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AE130" s="19" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="AF130" s="19" t="s">
         <v>48</v>
@@ -15046,22 +15046,22 @@
     </row>
     <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B131" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="D131" s="16" t="s">
         <v>701</v>
       </c>
-      <c r="C131" s="16" t="s">
+      <c r="E131" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="F131" s="16" t="s">
         <v>713</v>
-      </c>
-      <c r="D131" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="E131" s="16" t="s">
-        <v>714</v>
-      </c>
-      <c r="F131" s="16" t="s">
-        <v>715</v>
       </c>
       <c r="G131" s="16" t="s">
         <v>39</v>
@@ -15070,19 +15070,19 @@
         <v>40</v>
       </c>
       <c r="I131" s="17" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J131" s="16">
         <v>800000</v>
       </c>
       <c r="K131" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L131" s="16">
         <v>12000</v>
       </c>
       <c r="M131" s="16" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="N131" s="16" t="s">
         <v>43</v>
@@ -15108,13 +15108,13 @@
       <c r="AA131" s="16"/>
       <c r="AB131" s="19"/>
       <c r="AC131" s="19" t="s">
+        <v>716</v>
+      </c>
+      <c r="AD131" s="19" t="s">
+        <v>717</v>
+      </c>
+      <c r="AE131" s="19" t="s">
         <v>718</v>
-      </c>
-      <c r="AD131" s="19" t="s">
-        <v>719</v>
-      </c>
-      <c r="AE131" s="19" t="s">
-        <v>720</v>
       </c>
       <c r="AF131" s="19" t="s">
         <v>233</v>
@@ -15132,6 +15132,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15149,24 +15150,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>42</v>
@@ -15175,15 +15176,15 @@
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>85</v>
@@ -15192,338 +15193,338 @@
         <v>82</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>264</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>277</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>249</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>249</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>249</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>249</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>264</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>769</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>249</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>249</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>277</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>38</v>
@@ -15532,15 +15533,15 @@
         <v>38</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>82</v>
@@ -15549,15 +15550,15 @@
         <v>82</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>131</v>
@@ -15566,15 +15567,15 @@
         <v>131</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>157</v>
@@ -15583,15 +15584,15 @@
         <v>157</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>163</v>
@@ -15600,44 +15601,44 @@
         <v>163</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -15661,13 +15662,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -15675,13 +15676,13 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -15689,13 +15690,13 @@
         <v>139</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15703,13 +15704,13 @@
         <v>166</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -15717,13 +15718,13 @@
         <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>809</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -15737,7 +15738,7 @@
         <v>245</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -15745,13 +15746,13 @@
         <v>272</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>273</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -15759,111 +15760,111 @@
         <v>290</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>291</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>460</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>291</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>298</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>331</v>
-      </c>
       <c r="D11" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>363</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>384</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -15871,125 +15872,125 @@
         <v>297</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -16008,10 +16009,10 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -16049,170 +16050,170 @@
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
